--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62380.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62380.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,24 +671,23 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+      <c r="J3" t="n">
+        <v>242</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>KHz</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -696,7 +695,7 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
+      <c r="C5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -704,16 +703,7 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
       <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -721,15 +711,28 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62380.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62380.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>UJUJUUS UUUU N</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62380.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62380.xlsx
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
